--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008464239976449508</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>47252400</v>
+        <v>3773354</v>
       </c>
       <c r="L2" t="n">
-        <v>25114600</v>
+        <v>1734267</v>
       </c>
       <c r="M2" t="n">
-        <v>5832571</v>
+        <v>350084</v>
       </c>
       <c r="N2" t="n">
-        <v>169298</v>
+        <v>8094</v>
       </c>
       <c r="O2" t="n">
-        <v>3577971</v>
+        <v>227034</v>
       </c>
       <c r="P2" t="n">
-        <v>1277752</v>
+        <v>84465</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8343390226364136</v>
+        <v>0.7319683432579041</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6954577565193176</v>
+        <v>0.5290586352348328</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6149575710296631</v>
+        <v>0.4054798483848572</v>
       </c>
       <c r="U2" t="n">
-        <v>0.208852082490921</v>
+        <v>0.11123938113451</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6525732278823853</v>
+        <v>0.4560545682907104</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7726345062255859</v>
+        <v>0.5662369728088379</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029011818888065</v>
       </c>
       <c r="C3" t="n">
-        <v>3985</v>
+        <v>363</v>
       </c>
       <c r="D3" t="n">
-        <v>47252400</v>
+        <v>3773354</v>
       </c>
       <c r="E3" t="n">
-        <v>7444242</v>
+        <v>1089544</v>
       </c>
       <c r="F3" t="n">
-        <v>272060</v>
+        <v>66517</v>
       </c>
       <c r="G3" t="n">
-        <v>17805</v>
+        <v>4325</v>
       </c>
       <c r="H3" t="n">
-        <v>27309</v>
+        <v>8975</v>
       </c>
       <c r="I3" t="n">
-        <v>1895</v>
+        <v>878</v>
       </c>
       <c r="J3" t="n">
-        <v>110178607</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>115223773</v>
+        <v>10003920</v>
       </c>
       <c r="L3" t="n">
-        <v>132486036</v>
+        <v>11453328</v>
       </c>
       <c r="M3" t="n">
-        <v>165677352</v>
+        <v>14872546</v>
       </c>
       <c r="N3" t="n">
-        <v>178000762</v>
+        <v>16174972</v>
       </c>
       <c r="O3" t="n">
-        <v>172107773</v>
+        <v>15546309</v>
       </c>
       <c r="P3" t="n">
-        <v>177121047</v>
+        <v>16070964</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8588269948959351</v>
+        <v>0.7632256150245667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.694890022277832</v>
+        <v>0.5204078555107117</v>
       </c>
       <c r="T3" t="n">
-        <v>0.566472053527832</v>
+        <v>0.3709475696086884</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1721340864896774</v>
+        <v>0.0899733230471611</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6374512314796448</v>
+        <v>0.4429905712604523</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6002936363220215</v>
+        <v>0.4355392754077911</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8666099</v>
+        <v>1240588</v>
       </c>
       <c r="E4" t="n">
-        <v>25114600</v>
+        <v>1734267</v>
       </c>
       <c r="F4" t="n">
-        <v>1965620</v>
+        <v>272859</v>
       </c>
       <c r="G4" t="n">
-        <v>87099</v>
+        <v>15794</v>
       </c>
       <c r="H4" t="n">
-        <v>278756</v>
+        <v>61012</v>
       </c>
       <c r="I4" t="n">
-        <v>29661</v>
+        <v>7995</v>
       </c>
       <c r="J4" t="n">
-        <v>4235</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>9382131</v>
+        <v>1381724</v>
       </c>
       <c r="L4" t="n">
-        <v>10997729</v>
+        <v>1543757</v>
       </c>
       <c r="M4" t="n">
-        <v>3651939</v>
+        <v>513298</v>
       </c>
       <c r="N4" t="n">
-        <v>641314</v>
+        <v>64668</v>
       </c>
       <c r="O4" t="n">
-        <v>1904894</v>
+        <v>270788</v>
       </c>
       <c r="P4" t="n">
-        <v>376008</v>
+        <v>64704</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8464059233665466</v>
+        <v>0.7472702860832214</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6951737999916077</v>
+        <v>0.5246976017951965</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5897198915481567</v>
+        <v>0.3874458074569702</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1887237280607224</v>
+        <v>0.09948255121707916</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6449235677719116</v>
+        <v>0.4494276642799377</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6756472587585449</v>
+        <v>0.4923623204231262</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>508242</v>
+        <v>104524</v>
       </c>
       <c r="E5" t="n">
-        <v>2886376</v>
+        <v>336483</v>
       </c>
       <c r="F5" t="n">
-        <v>5832571</v>
+        <v>350084</v>
       </c>
       <c r="G5" t="n">
-        <v>197130</v>
+        <v>21029</v>
       </c>
       <c r="H5" t="n">
-        <v>784696</v>
+        <v>113757</v>
       </c>
       <c r="I5" t="n">
-        <v>87294</v>
+        <v>17879</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7767296</v>
+        <v>1170602</v>
       </c>
       <c r="L5" t="n">
-        <v>11027235</v>
+        <v>1598248</v>
       </c>
       <c r="M5" t="n">
-        <v>4463738</v>
+        <v>593672</v>
       </c>
       <c r="N5" t="n">
-        <v>814226</v>
+        <v>81866</v>
       </c>
       <c r="O5" t="n">
-        <v>2034962</v>
+        <v>285469</v>
       </c>
       <c r="P5" t="n">
-        <v>850793</v>
+        <v>109467</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9045268297195435</v>
+        <v>0.8436993956565857</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8773840665817261</v>
+        <v>0.8075883388519287</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9548189043998718</v>
+        <v>0.9322108030319214</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9918968081474304</v>
+        <v>0.9910264611244202</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9780662655830383</v>
+        <v>0.9659356474876404</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931702613830566</v>
+        <v>0.9893340468406677</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>159970</v>
+        <v>19824</v>
       </c>
       <c r="E6" t="n">
-        <v>233932</v>
+        <v>25128</v>
       </c>
       <c r="F6" t="n">
-        <v>294512</v>
+        <v>22357</v>
       </c>
       <c r="G6" t="n">
-        <v>169298</v>
+        <v>8094</v>
       </c>
       <c r="H6" t="n">
-        <v>114847</v>
+        <v>12624</v>
       </c>
       <c r="I6" t="n">
-        <v>10736</v>
+        <v>1912</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>45226</v>
+        <v>15570</v>
       </c>
       <c r="E7" t="n">
-        <v>393950</v>
+        <v>82205</v>
       </c>
       <c r="F7" t="n">
-        <v>1033400</v>
+        <v>131822</v>
       </c>
       <c r="G7" t="n">
-        <v>315964</v>
+        <v>19832</v>
       </c>
       <c r="H7" t="n">
-        <v>3577971</v>
+        <v>227034</v>
       </c>
       <c r="I7" t="n">
-        <v>246422</v>
+        <v>36040</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2594</v>
+        <v>1218</v>
       </c>
       <c r="E8" t="n">
-        <v>39229</v>
+        <v>10397</v>
       </c>
       <c r="F8" t="n">
-        <v>86347</v>
+        <v>19743</v>
       </c>
       <c r="G8" t="n">
-        <v>23316</v>
+        <v>3688</v>
       </c>
       <c r="H8" t="n">
-        <v>699286</v>
+        <v>74420</v>
       </c>
       <c r="I8" t="n">
-        <v>1277752</v>
+        <v>84465</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
